--- a/bestellijst.xlsx
+++ b/bestellijst.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bestellijst" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bestellijst'!$A$4:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bestellijst'!$A$4:$J$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>LILYGO T-Panel S3, CAN-versie (H720)</t>
+          <t>Waveshare ESP32-S3-Touch-LCD-4 (touchversie)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -565,19 +565,19 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Het scherm met de ESP32-S3 en de CAN-aansluiting voor NMEA 2000</t>
+          <t>Het scherm met de ESP32-S3; CAN voor NMEA 2000, klok, zoemer en micro-SD zitten erop</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>T-Panel S3 H720 CAN FD</t>
+          <t>Waveshare ESP32-S3-Touch-LCD-4</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>55</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>90</v>
       </c>
       <c r="H5" s="6">
         <f>B5*F5</f>
@@ -589,14 +589,14 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Kies bewust H720 (CAN FD). De RS485-versie (H719) heeft geen CAN.</t>
+          <t>Neem de touchversie. Niet de -4B: die heeft geen CAN en geen 12 V-ingang.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>DS3231 RTC-module met CR2032-houder</t>
+          <t>Oplaadbare RTC-cel (ML1220) met stekkertje</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -609,19 +609,19 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Bewaart de tijd ook zonder stroom</t>
+          <t>Houdt de klok gaande zonder stroom</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>DS3231 RTC module CR2032</t>
+          <t>Waveshare RTC battery ML1220</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="6">
         <f>B6*F6</f>
@@ -633,14 +633,14 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Controleer of de module een laadcircuit heeft (ZS-042). Zie de README over het diodetje/de weerstand.</t>
+          <t>Als optie bij Waveshare mee te bestellen. Geen gewone CR2032: het board laadt de cel bij.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>CR2032 knoopcel</t>
+          <t>Zekering 1 A met houder</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
@@ -653,19 +653,19 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Voeding voor de klok</t>
+          <t>Beveiliging van de 12 V-voeding van het board</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>CR2032 3V lithium</t>
+          <t>inline fuse holder 1A blade</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H7" s="6">
         <f>B7*F7</f>
@@ -677,14 +677,14 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Neem een setje van 5. Ook voor later.</t>
+          <t>Plaats dicht bij de accu.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>I2C LCD-backpack PCF8574 (voor 1602/2004)</t>
+          <t>Draad 1 mm² en 2,5 mm², met krimpkousen en kabelschoenen</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -697,19 +697,19 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Biedt de I2C-poort en de pinnen voor de zoemer. Het LCD-scherm zelf hoef je niet te kopen.</t>
+          <t>Voeding en signaalbedrading</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>PCF8574 I2C LCD backpack 1602</t>
+          <t>kabelschoen krimpset</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H8" s="6">
         <f>B8*F8</f>
@@ -721,14 +721,14 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Met de 16-polige header; de pinnen 15 en 16 zijn nodig voor de zoemer.</t>
+          <t>De stroomdraad naar de klem 2,5 mm² of dikker.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Actieve zoemer 3-5 V</t>
+          <t>NMEA 2000 drop-kabel met M12-stekker</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -741,19 +741,19 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Piept bij een rood alarm</t>
+          <t>Verbindt het board met de bus van je boot</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>active buzzer 5V</t>
+          <t>NMEA 2000 drop cable M12 female</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="H9" s="6">
         <f>B9*F9</f>
@@ -765,14 +765,14 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Actief, dus met een eigen oscillator. Een passieve zoemer piept niet vanzelf.</t>
+          <t>Een kabel met één open einde. Lengte: tot aan de bus.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Zekering 1 A met houder</t>
+          <t>NMEA 2000 T-stuk of afsluiter</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -780,24 +780,24 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Soms nodig</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Beveiliging van de 12 V-voeding van het board</t>
+          <t>Zodat je kabel op de bus kan zitten</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>inline fuse holder 1A blade</t>
+          <t>NMEA 2000 T-piece</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H10" s="6">
         <f>B10*F10</f>
@@ -809,14 +809,14 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Plaats dicht bij de accu.</t>
+          <t>Let op: er mag maar één afsluiter per uiteinde van de bus zitten.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Draad 1 mm² en 2,5 mm², met krimpkousen en kabelschoenen</t>
+          <t>USB-C datakabel</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -829,19 +829,19 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Voeding en signaalbedrading</t>
+          <t>Firmware zetten en de seriële log bekijken</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>kabelschoen krimpset</t>
+          <t>USB-C datakabel</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H11" s="6">
         <f>B11*F11</f>
@@ -853,14 +853,14 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>De stroomdraad naar de klem 2,5 mm² of dikker.</t>
+          <t>Een kabel die data kan, geen alleen-laadkabel.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>NMEA 2000 drop-kabel met M12-stekker</t>
+          <t>Multimeter</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -868,24 +868,24 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Ja (CAN-versie)</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Verbindt de T-Panel met de bus van je boot</t>
+          <t>Controleren van spanning, de bus en de afsluitweerstand (60 Ω)</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>NMEA 2000 drop cable M12 female</t>
+          <t>multimeter</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H12" s="6">
         <f>B12*F12</f>
@@ -897,14 +897,14 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Een kabel met één open einde. Lengte: tot aan de bus.</t>
+          <t>Een gewone multimeter is genoeg.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>NMEA 2000 T-stuk of afsluiter</t>
+          <t>Micro-SD-kaart (FAT32, tot 32 GB)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -912,24 +912,24 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Soms nodig</t>
+          <t>Optioneel</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Zodat je kabel op de bus kan zitten</t>
+          <t>Metingen, logboek en backups</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>NMEA 2000 T-piece</t>
+          <t>micro SD 16GB</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="6" t="n">
         <v>10</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>20</v>
       </c>
       <c r="H13" s="6">
         <f>B13*F13</f>
@@ -941,36 +941,36 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Let op: er mag maar één afsluiter per uiteinde van de bus zitten.</t>
+          <t>Een kaart van 8 tot 32 GB is ruim genoeg.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>USB-C datakabel</t>
+          <t>BME280-module (luchtdruk)</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Optioneel</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Firmware zetten en de seriële log bekijken</t>
+          <t>Barometer en stormwaarschuwing</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>USB-C datakabel</t>
+          <t>BME280 I2C module</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>8</v>
@@ -985,39 +985,39 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Een kabel die data kan, geen alleen-laadkabel.</t>
+          <t>Aantal 0: zelf optellen. Op de I2C-klem van het board.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Multimeter</t>
+          <t>Ruuvi-tag (temperatuur/vocht)</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Optioneel</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Controleren van spanning, de bus en de afsluitweerstand (60 Ω)</t>
+          <t>Draadloze thermometer, bv. voor de koelkast</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>multimeter</t>
+          <t>RuuviTag</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H15" s="6">
         <f>B15*F15</f>
@@ -1029,14 +1029,14 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Een gewone multimeter is genoeg.</t>
+          <t>Aantal 0: per stuk zelf optellen. Geen bedrading, geen sleutel.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ruuvi-tag (temperatuur/vocht)</t>
+          <t>Xiaomi LYWSD03MMC thermometer</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1049,19 +1049,19 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Draadloze thermometer, bv. voor de koelkast</t>
+          <t>Goedkope draadloze thermometer</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>RuuviTag</t>
+          <t>LYWSD03MMC</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H16" s="6">
         <f>B16*F16</f>
@@ -1073,14 +1073,14 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Aantal 0: per stuk zelf optellen. Geen bedrading, geen sleutel.</t>
+          <t>Aantal 0: per stuk zelf optellen. Eerst de ATC-firmware flashen; zie de README.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Xiaomi LYWSD03MMC thermometer</t>
+          <t>Mopeka Pro Check tanksensor</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -1093,19 +1093,19 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Goedkope draadloze thermometer</t>
+          <t>Tankniveau via de tankwand, bv. gas, water of diesel</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>LYWSD03MMC</t>
+          <t>Mopeka Pro Check</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="H17" s="6">
         <f>B17*F17</f>
@@ -1117,39 +1117,39 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Aantal 0: per stuk zelf optellen. Eerst de ATC-firmware flashen; zie de README.</t>
+          <t>Aantal 0: per tank zelf optellen. Kalibreren op vol en leeg.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Mopeka Pro Check tanksensor</t>
+          <t>Behuizing (3D-print)</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Optioneel</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Opbouw tegen een wand of inbouw in een schot</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>PETG of ASA filament</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Optioneel</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Tankniveau via de tankwand, bv. gas (propaan)</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Mopeka Pro Check</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>45</v>
-      </c>
       <c r="G18" s="6" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="H18" s="6">
         <f>B18*F18</f>
@@ -1161,86 +1161,42 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Aantal 0: per tank zelf optellen. Kalibreren op vol en leeg.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Montagebeugel of kast voor het scherm</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Optioneel</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Het board vastzetten</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>T-Panel mounting bracket</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="H19" s="6">
-        <f>B19*F19</f>
-        <v/>
-      </c>
-      <c r="I19" s="6">
-        <f>B19*G19</f>
-        <v/>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>Het project bevat ook behuizingsbestanden in de map structure.</t>
-        </is>
+          <t>Ontwerp in de map enclosure van het project; print in PETG of ASA (PLA wordt te zacht in de zon).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Totaal verplicht</t>
+        </is>
+      </c>
+      <c r="H20" s="8">
+        <f>SUMIF(C5:C18,"Ja*",H5:H18)</f>
+        <v/>
+      </c>
+      <c r="I20" s="8">
+        <f>SUMIF(C5:C18,"Ja*",I5:I18)</f>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Totaal verplicht</t>
-        </is>
-      </c>
-      <c r="H21" s="8">
-        <f>SUMIF(C5:C19,"Ja*",H5:H19)</f>
-        <v/>
-      </c>
-      <c r="I21" s="8">
-        <f>SUMIF(C5:C19,"Ja*",I5:I19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Totaal soms nodig en optioneel (sensoren tellen per stuk, zie opmerking)</t>
         </is>
       </c>
-      <c r="H22" s="9">
-        <f>SUM(H5:H19)-H21</f>
-        <v/>
-      </c>
-      <c r="I22" s="9">
-        <f>SUM(I5:I19)-I21</f>
+      <c r="H21" s="9">
+        <f>SUM(H5:H18)-H20</f>
+        <v/>
+      </c>
+      <c r="I21" s="9">
+        <f>SUM(I5:I18)-I20</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J19"/>
+  <autoFilter ref="A4:J18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/bestellijst.xlsx
+++ b/bestellijst.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Als optie bij Waveshare mee te bestellen. Geen gewone CR2032: het board laadt de cel bij.</t>
+          <t>Sterk aangeraden: zonder cel is de tijd na elke stroomuitval weg. Als optie bij Waveshare mee te bestellen. Geen gewone CR2032: het board laadt de cel bij.</t>
         </is>
       </c>
     </row>

--- a/bestellijst.xlsx
+++ b/bestellijst.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bestellijst" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bestellijst'!$A$4:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bestellijst'!$A$4:$J$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -728,7 +728,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>NMEA 2000 drop-kabel met M12-stekker</t>
+          <t>Adereindhulzen 0,25–1,5 mm² met krimptang (set)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
@@ -741,16 +741,16 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Verbindt het board met de bus van je boot</t>
+          <t>Op elke draad in de schroefklem: blijft vast bij trillingen</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>NMEA 2000 drop cable M12 female</t>
+          <t>adereindhulzen set krimptang</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>30</v>
@@ -765,14 +765,14 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Een kabel met één open einde. Lengte: tot aan de bus.</t>
+          <t>Ook 0,25 mm² voor de dunne sensorkabel en een paar dubbele (twin) hulzen 2 × 0,5 mm².</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>NMEA 2000 T-stuk of afsluiter</t>
+          <t>NMEA 2000 drop-kabel met M12-stekker</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -780,24 +780,24 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Soms nodig</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Zodat je kabel op de bus kan zitten</t>
+          <t>Verbindt het board met de bus van je boot</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>NMEA 2000 T-piece</t>
+          <t>NMEA 2000 drop cable M12 female</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H10" s="6">
         <f>B10*F10</f>
@@ -809,14 +809,14 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Let op: er mag maar één afsluiter per uiteinde van de bus zitten.</t>
+          <t>Een kabel met één open einde. Lengte: tot aan de bus.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>USB-C datakabel</t>
+          <t>NMEA 2000 T-stuk of afsluiter</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
@@ -824,24 +824,24 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Soms nodig</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Firmware zetten en de seriële log bekijken</t>
+          <t>Zodat je kabel op de bus kan zitten</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>USB-C datakabel</t>
+          <t>NMEA 2000 T-piece</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H11" s="6">
         <f>B11*F11</f>
@@ -853,14 +853,14 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Een kabel die data kan, geen alleen-laadkabel.</t>
+          <t>Let op: er mag maar één afsluiter per uiteinde van de bus zitten.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Multimeter</t>
+          <t>USB-C datakabel</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -873,19 +873,19 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Controleren van spanning, de bus en de afsluitweerstand (60 Ω)</t>
+          <t>Firmware zetten en de seriële log bekijken</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>multimeter</t>
+          <t>USB-C datakabel</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H12" s="6">
         <f>B12*F12</f>
@@ -897,14 +897,14 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Een gewone multimeter is genoeg.</t>
+          <t>Een kabel die data kan, geen alleen-laadkabel.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Micro-SD-kaart (FAT32, tot 32 GB)</t>
+          <t>Multimeter</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
@@ -912,24 +912,24 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Optioneel</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Metingen, logboek en backups</t>
+          <t>Controleren van spanning, de bus en de afsluitweerstand (60 Ω)</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>micro SD 16GB</t>
+          <t>multimeter</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H13" s="6">
         <f>B13*F13</f>
@@ -941,18 +941,18 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Een kaart van 8 tot 32 GB is ruim genoeg.</t>
+          <t>Een gewone multimeter is genoeg.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>BME280-module (luchtdruk)</t>
+          <t>Micro-SD-kaart (FAT32, tot 32 GB)</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Barometer en stormwaarschuwing</t>
+          <t>Metingen, logboek en backups</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>BME280 I2C module</t>
+          <t>micro SD 16GB</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H14" s="6">
         <f>B14*F14</f>
@@ -985,14 +985,14 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Aantal 0: zelf optellen. Op de I2C-klem van het board.</t>
+          <t>Een kaart van 8 tot 32 GB is ruim genoeg.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Ruuvi-tag (temperatuur/vocht)</t>
+          <t>DFRobot Gravity BME280 (SEN0236)</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -1005,19 +1005,19 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Draadloze thermometer, bv. voor de koelkast</t>
+          <t>Barometer en stormwaarschuwing (luchtdruk, ook vocht en temperatuur)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>RuuviTag</t>
+          <t>DFRobot SEN0236</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="H15" s="6">
         <f>B15*F15</f>
@@ -1029,14 +1029,14 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Aantal 0: per stuk zelf optellen. Geen bedrading, geen sleutel.</t>
+          <t>Aantal 0: zelf optellen. Vergrendelende stekker, niets solderen. Dupont-stekkertje van de kabel afknippen, adereindhulzen erop, in de I2C-klem.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Xiaomi LYWSD03MMC thermometer</t>
+          <t>Ruuvi-tag (temperatuur/vocht)</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1049,19 +1049,19 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Goedkope draadloze thermometer</t>
+          <t>Draadloze thermometer, bv. voor de koelkast</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>LYWSD03MMC</t>
+          <t>RuuviTag</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H16" s="6">
         <f>B16*F16</f>
@@ -1073,14 +1073,14 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Aantal 0: per stuk zelf optellen. Eerst de ATC-firmware flashen; zie de README.</t>
+          <t>Aantal 0: per stuk zelf optellen. Geen bedrading, geen sleutel.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Mopeka Pro Check tanksensor</t>
+          <t>Xiaomi LYWSD03MMC thermometer</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -1093,19 +1093,19 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Tankniveau via de tankwand, bv. gas, water of diesel</t>
+          <t>Goedkope draadloze thermometer</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Mopeka Pro Check</t>
+          <t>LYWSD03MMC</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="H17" s="6">
         <f>B17*F17</f>
@@ -1117,18 +1117,18 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Aantal 0: per tank zelf optellen. Kalibreren op vol en leeg.</t>
+          <t>Aantal 0: per stuk zelf optellen. Eerst de ATC-firmware flashen; zie de README.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Behuizing (3D-print)</t>
+          <t>Mopeka Pro Check tanksensor</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Opbouw tegen een wand of inbouw in een schot</t>
+          <t>Tankniveau via de tankwand, bv. gas, water of diesel</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>PETG of ASA filament</t>
+          <t>Mopeka Pro Check</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="H18" s="6">
         <f>B18*F18</f>
@@ -1161,42 +1161,86 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
+          <t>Aantal 0: per tank zelf optellen. Kalibreren op vol en leeg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Behuizing (3D-print)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Optioneel</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Opbouw tegen een wand of inbouw in een schot</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>PETG of ASA filament</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="6">
+        <f>B19*F19</f>
+        <v/>
+      </c>
+      <c r="I19" s="6">
+        <f>B19*G19</f>
+        <v/>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
           <t>Ontwerp in de map enclosure van het project; print in PETG of ASA (PLA wordt te zacht in de zon).</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Totaal verplicht</t>
         </is>
       </c>
-      <c r="H20" s="8">
-        <f>SUMIF(C5:C18,"Ja*",H5:H18)</f>
-        <v/>
-      </c>
-      <c r="I20" s="8">
-        <f>SUMIF(C5:C18,"Ja*",I5:I18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="H21" s="8">
+        <f>SUMIF(C5:C19,"Ja*",H5:H19)</f>
+        <v/>
+      </c>
+      <c r="I21" s="8">
+        <f>SUMIF(C5:C19,"Ja*",I5:I19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Totaal soms nodig en optioneel (sensoren tellen per stuk, zie opmerking)</t>
         </is>
       </c>
-      <c r="H21" s="9">
-        <f>SUM(H5:H18)-H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="9">
-        <f>SUM(I5:I18)-I20</f>
+      <c r="H22" s="9">
+        <f>SUM(H5:H19)-H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="9">
+        <f>SUM(I5:I19)-I21</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J18"/>
+  <autoFilter ref="A4:J19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/bestellijst.xlsx
+++ b/bestellijst.xlsx
@@ -596,7 +596,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Oplaadbare RTC-cel (ML1220) met stekkertje</t>
+          <t>Oplaadbare RTC-cel ML2032/ML2020 met JST-SH-stekker</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -614,14 +614,14 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Waveshare RTC battery ML1220</t>
+          <t>Raspberry Pi 5 RTC battery ML2032</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H6" s="6">
         <f>B6*F6</f>
@@ -633,7 +633,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Sterk aangeraden: zonder cel is de tijd na elke stroomuitval weg. Als optie bij Waveshare mee te bestellen. Geen gewone CR2032: het board laadt de cel bij.</t>
+          <t>Sterk aangeraden: zonder cel is de tijd na elke stroomuitval weg. Zoals de RTC-batterij voor de Raspberry Pi 5. Controleer voor het insteken dat rood bij de + of 1 op het board uitkomt. Geen gewone CR2032.</t>
         </is>
       </c>
     </row>
